--- a/src/main/resources/FeatureFiles/DownloadPageServerTabTestCases.xlsx
+++ b/src/main/resources/FeatureFiles/DownloadPageServerTabTestCases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gurcharan/Desktop/CouchBase/src/main/resources/FeatureFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66E904E-8C13-5D4E-B283-053C0A6274E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088F1AF0-FA88-7642-B1AB-BF1B7D9E6C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="16920" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
@@ -303,9 +303,6 @@
     <t>DownloadServerPage_Community_Header</t>
   </si>
   <si>
-    <t>7.6.2 (Current)</t>
-  </si>
-  <si>
     <t>DownloadServerPage_Community_Button_Download</t>
   </si>
   <si>
@@ -424,6 +421,9 @@
   </si>
   <si>
     <t>Tags</t>
+  </si>
+  <si>
+    <t>7.6.2</t>
   </si>
 </sst>
 </file>
@@ -828,7 +828,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -839,7 +839,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E2" s="2"/>
     </row>
@@ -848,7 +848,7 @@
         <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -5159,13 +5159,13 @@
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A453" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.2">
@@ -5173,7 +5173,7 @@
         <v>9</v>
       </c>
       <c r="C454" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.2">
@@ -5181,7 +5181,7 @@
         <v>4</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.2">
@@ -5189,10 +5189,10 @@
         <v>7</v>
       </c>
       <c r="C456" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.2">
@@ -5200,10 +5200,10 @@
         <v>7</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.2">
@@ -5211,7 +5211,7 @@
         <v>9</v>
       </c>
       <c r="C458" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.2">
@@ -5364,7 +5364,7 @@
         <v>9</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D473" s="3"/>
     </row>
@@ -5389,13 +5389,13 @@
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A477" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.2">
@@ -5403,7 +5403,7 @@
         <v>9</v>
       </c>
       <c r="C478" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.2">
@@ -5411,7 +5411,7 @@
         <v>4</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.2">
@@ -5419,10 +5419,10 @@
         <v>7</v>
       </c>
       <c r="C480" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="481" spans="2:4" x14ac:dyDescent="0.2">
@@ -5430,10 +5430,10 @@
         <v>7</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="482" spans="2:4" x14ac:dyDescent="0.2">
@@ -5441,7 +5441,7 @@
         <v>9</v>
       </c>
       <c r="C482" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="483" spans="2:4" x14ac:dyDescent="0.2">
@@ -5625,7 +5625,7 @@
         <v>9</v>
       </c>
       <c r="C500" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D500" s="3"/>
     </row>
@@ -5650,13 +5650,13 @@
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A504" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C504" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.2">
@@ -5664,7 +5664,7 @@
         <v>9</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.2">
@@ -5672,7 +5672,7 @@
         <v>4</v>
       </c>
       <c r="C506" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.2">
@@ -5680,10 +5680,10 @@
         <v>7</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D507" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.2">
@@ -5691,10 +5691,10 @@
         <v>7</v>
       </c>
       <c r="C508" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D508" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.2">
@@ -5702,7 +5702,7 @@
         <v>9</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.2">
@@ -5874,7 +5874,7 @@
         <v>4</v>
       </c>
       <c r="C526" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D526" s="5"/>
     </row>
@@ -5883,7 +5883,7 @@
         <v>9</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D527" s="5"/>
     </row>
@@ -5892,7 +5892,7 @@
         <v>9</v>
       </c>
       <c r="C528" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D528" s="3"/>
     </row>
@@ -5919,13 +5919,13 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A532" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C532" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.2">
@@ -5933,7 +5933,7 @@
         <v>9</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.2">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C534" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.2">
@@ -5949,10 +5949,10 @@
         <v>7</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D535" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.2">
@@ -5960,10 +5960,10 @@
         <v>7</v>
       </c>
       <c r="C536" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D536" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.2">
@@ -5971,7 +5971,7 @@
         <v>9</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.2">
@@ -6102,7 +6102,7 @@
         <v>9</v>
       </c>
       <c r="C550" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D550" s="3"/>
     </row>
@@ -6124,13 +6124,13 @@
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A554" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C554" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.2">
@@ -6138,7 +6138,7 @@
         <v>9</v>
       </c>
       <c r="C555" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.2">
@@ -6146,7 +6146,7 @@
         <v>4</v>
       </c>
       <c r="C556" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.2">
@@ -6154,10 +6154,10 @@
         <v>7</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D557" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.2">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="C558" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.2">
@@ -6176,7 +6176,7 @@
         <v>9</v>
       </c>
       <c r="C559" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.2">
@@ -6307,7 +6307,7 @@
         <v>9</v>
       </c>
       <c r="C572" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D572" s="3"/>
     </row>
@@ -6329,13 +6329,13 @@
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A576" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C576" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="577" spans="2:4" x14ac:dyDescent="0.2">
@@ -6343,7 +6343,7 @@
         <v>9</v>
       </c>
       <c r="C577" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="578" spans="2:4" x14ac:dyDescent="0.2">
@@ -6351,7 +6351,7 @@
         <v>4</v>
       </c>
       <c r="C578" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="579" spans="2:4" x14ac:dyDescent="0.2">
@@ -6359,10 +6359,10 @@
         <v>7</v>
       </c>
       <c r="C579" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D579" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="580" spans="2:4" x14ac:dyDescent="0.2">
@@ -6370,10 +6370,10 @@
         <v>7</v>
       </c>
       <c r="C580" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="581" spans="2:4" x14ac:dyDescent="0.2">
@@ -6381,7 +6381,7 @@
         <v>9</v>
       </c>
       <c r="C581" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="582" spans="2:4" x14ac:dyDescent="0.2">
@@ -6512,7 +6512,7 @@
         <v>9</v>
       </c>
       <c r="C594" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D594" s="3"/>
     </row>
@@ -6534,13 +6534,13 @@
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A598" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C598" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.2">
@@ -6548,7 +6548,7 @@
         <v>9</v>
       </c>
       <c r="C599" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.2">
@@ -6556,7 +6556,7 @@
         <v>4</v>
       </c>
       <c r="C600" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.2">
@@ -6564,10 +6564,10 @@
         <v>7</v>
       </c>
       <c r="C601" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D601" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.2">
@@ -6575,10 +6575,10 @@
         <v>7</v>
       </c>
       <c r="C602" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D602" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.2">
@@ -6586,7 +6586,7 @@
         <v>9</v>
       </c>
       <c r="C603" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.2">
@@ -6717,7 +6717,7 @@
         <v>9</v>
       </c>
       <c r="C616" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D616" s="3"/>
     </row>
@@ -6742,13 +6742,13 @@
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A620" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B620" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C620" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.2">
@@ -6756,7 +6756,7 @@
         <v>9</v>
       </c>
       <c r="C621" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.2">
@@ -6764,7 +6764,7 @@
         <v>4</v>
       </c>
       <c r="C622" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.2">
@@ -6772,10 +6772,10 @@
         <v>7</v>
       </c>
       <c r="C623" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D623" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.2">
@@ -6783,10 +6783,10 @@
         <v>7</v>
       </c>
       <c r="C624" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D624" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="625" spans="2:4" x14ac:dyDescent="0.2">
@@ -6794,7 +6794,7 @@
         <v>9</v>
       </c>
       <c r="C625" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="626" spans="2:4" x14ac:dyDescent="0.2">
@@ -6925,7 +6925,7 @@
         <v>9</v>
       </c>
       <c r="C638" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D638" s="3"/>
     </row>
@@ -6951,13 +6951,13 @@
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A642" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B642" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C642" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.2">
@@ -6965,7 +6965,7 @@
         <v>9</v>
       </c>
       <c r="C643" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.2">
@@ -6973,7 +6973,7 @@
         <v>4</v>
       </c>
       <c r="C644" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.2">
@@ -6981,10 +6981,10 @@
         <v>7</v>
       </c>
       <c r="C645" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D645" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.2">
@@ -6992,10 +6992,10 @@
         <v>7</v>
       </c>
       <c r="C646" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D646" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.2">
@@ -7003,7 +7003,7 @@
         <v>9</v>
       </c>
       <c r="C647" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.2">
@@ -7156,7 +7156,7 @@
         <v>9</v>
       </c>
       <c r="C662" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D662" s="3"/>
     </row>
@@ -7181,13 +7181,13 @@
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A666" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C666" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.2">
@@ -7195,7 +7195,7 @@
         <v>9</v>
       </c>
       <c r="C667" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.2">
@@ -7203,7 +7203,7 @@
         <v>4</v>
       </c>
       <c r="C668" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.2">
@@ -7211,10 +7211,10 @@
         <v>7</v>
       </c>
       <c r="C669" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D669" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.2">
@@ -7222,10 +7222,10 @@
         <v>7</v>
       </c>
       <c r="C670" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D670" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.2">
@@ -7233,7 +7233,7 @@
         <v>9</v>
       </c>
       <c r="C671" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.2">
@@ -7375,7 +7375,7 @@
         <v>9</v>
       </c>
       <c r="C685" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D685" s="3"/>
     </row>
@@ -7400,13 +7400,13 @@
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A689" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B689" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C689" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.2">
@@ -7414,7 +7414,7 @@
         <v>9</v>
       </c>
       <c r="C690" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.2">
@@ -7422,7 +7422,7 @@
         <v>4</v>
       </c>
       <c r="C691" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.2">
@@ -7430,10 +7430,10 @@
         <v>7</v>
       </c>
       <c r="C692" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D692" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.2">
@@ -7441,10 +7441,10 @@
         <v>7</v>
       </c>
       <c r="C693" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D693" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.2">
@@ -7452,7 +7452,7 @@
         <v>9</v>
       </c>
       <c r="C694" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.2">
@@ -7622,13 +7622,13 @@
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A712" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B712" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C712" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.2">
@@ -7636,7 +7636,7 @@
         <v>9</v>
       </c>
       <c r="C713" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.2">
@@ -7644,7 +7644,7 @@
         <v>4</v>
       </c>
       <c r="C714" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.2">
@@ -7652,10 +7652,10 @@
         <v>7</v>
       </c>
       <c r="C715" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D715" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.2">
@@ -7663,10 +7663,10 @@
         <v>7</v>
       </c>
       <c r="C716" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D716" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.2">
@@ -7674,7 +7674,7 @@
         <v>9</v>
       </c>
       <c r="C717" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.2">
@@ -7827,7 +7827,7 @@
         <v>9</v>
       </c>
       <c r="C732" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D732" s="3"/>
     </row>
@@ -7852,13 +7852,13 @@
     </row>
     <row r="736" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A736" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B736" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C736" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="737" spans="2:4" x14ac:dyDescent="0.2">
@@ -7866,7 +7866,7 @@
         <v>9</v>
       </c>
       <c r="C737" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="738" spans="2:4" x14ac:dyDescent="0.2">
@@ -7874,7 +7874,7 @@
         <v>4</v>
       </c>
       <c r="C738" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="739" spans="2:4" x14ac:dyDescent="0.2">
@@ -7882,10 +7882,10 @@
         <v>7</v>
       </c>
       <c r="C739" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D739" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="740" spans="2:4" x14ac:dyDescent="0.2">
@@ -7893,10 +7893,10 @@
         <v>7</v>
       </c>
       <c r="C740" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D740" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="741" spans="2:4" x14ac:dyDescent="0.2">
@@ -7904,7 +7904,7 @@
         <v>9</v>
       </c>
       <c r="C741" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="742" spans="2:4" x14ac:dyDescent="0.2">
@@ -8057,7 +8057,7 @@
         <v>4</v>
       </c>
       <c r="C756" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D756" s="5"/>
     </row>
@@ -8066,7 +8066,7 @@
         <v>9</v>
       </c>
       <c r="C757" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D757" s="5"/>
     </row>
@@ -8075,7 +8075,7 @@
         <v>9</v>
       </c>
       <c r="C758" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D758" s="3"/>
     </row>
@@ -8101,13 +8101,13 @@
     </row>
     <row r="762" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A762" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B762" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C762" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="763" spans="1:4" x14ac:dyDescent="0.2">
@@ -8115,7 +8115,7 @@
         <v>9</v>
       </c>
       <c r="C763" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="764" spans="1:4" x14ac:dyDescent="0.2">
@@ -8123,7 +8123,7 @@
         <v>4</v>
       </c>
       <c r="C764" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="765" spans="1:4" x14ac:dyDescent="0.2">
@@ -8131,10 +8131,10 @@
         <v>7</v>
       </c>
       <c r="C765" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D765" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="766" spans="1:4" x14ac:dyDescent="0.2">
@@ -8142,10 +8142,10 @@
         <v>7</v>
       </c>
       <c r="C766" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D766" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="767" spans="1:4" x14ac:dyDescent="0.2">
@@ -8153,7 +8153,7 @@
         <v>9</v>
       </c>
       <c r="C767" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="768" spans="1:4" x14ac:dyDescent="0.2">
@@ -8306,7 +8306,7 @@
         <v>9</v>
       </c>
       <c r="C782" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D782" s="3"/>
     </row>
@@ -8333,13 +8333,13 @@
     </row>
     <row r="786" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A786" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B786" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C786" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="787" spans="1:4" x14ac:dyDescent="0.2">
@@ -8347,7 +8347,7 @@
         <v>9</v>
       </c>
       <c r="C787" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="788" spans="1:4" x14ac:dyDescent="0.2">
@@ -8355,7 +8355,7 @@
         <v>4</v>
       </c>
       <c r="C788" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="789" spans="1:4" x14ac:dyDescent="0.2">
@@ -8363,10 +8363,10 @@
         <v>7</v>
       </c>
       <c r="C789" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D789" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="790" spans="1:4" x14ac:dyDescent="0.2">
@@ -8374,10 +8374,10 @@
         <v>7</v>
       </c>
       <c r="C790" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D790" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="791" spans="1:4" x14ac:dyDescent="0.2">
@@ -8385,7 +8385,7 @@
         <v>9</v>
       </c>
       <c r="C791" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="792" spans="1:4" x14ac:dyDescent="0.2">
@@ -8538,7 +8538,7 @@
         <v>9</v>
       </c>
       <c r="C806" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D806" s="3"/>
     </row>
@@ -8560,13 +8560,13 @@
     </row>
     <row r="810" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A810" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B810" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C810" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="811" spans="1:4" x14ac:dyDescent="0.2">
@@ -8574,7 +8574,7 @@
         <v>9</v>
       </c>
       <c r="C811" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="812" spans="1:4" x14ac:dyDescent="0.2">
@@ -8582,7 +8582,7 @@
         <v>4</v>
       </c>
       <c r="C812" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="813" spans="1:4" x14ac:dyDescent="0.2">
@@ -8590,10 +8590,10 @@
         <v>7</v>
       </c>
       <c r="C813" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D813" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="814" spans="1:4" x14ac:dyDescent="0.2">
@@ -8601,10 +8601,10 @@
         <v>7</v>
       </c>
       <c r="C814" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D814" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="815" spans="1:4" x14ac:dyDescent="0.2">
@@ -8612,7 +8612,7 @@
         <v>9</v>
       </c>
       <c r="C815" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="816" spans="1:4" x14ac:dyDescent="0.2">
@@ -8765,7 +8765,7 @@
         <v>9</v>
       </c>
       <c r="C830" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D830" s="3"/>
     </row>
@@ -8787,13 +8787,13 @@
     </row>
     <row r="834" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A834" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B834" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C834" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="835" spans="1:4" x14ac:dyDescent="0.2">
@@ -8801,7 +8801,7 @@
         <v>9</v>
       </c>
       <c r="C835" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="836" spans="1:4" x14ac:dyDescent="0.2">
@@ -8809,7 +8809,7 @@
         <v>4</v>
       </c>
       <c r="C836" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="837" spans="1:4" x14ac:dyDescent="0.2">
@@ -8817,10 +8817,10 @@
         <v>7</v>
       </c>
       <c r="C837" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D837" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="838" spans="1:4" x14ac:dyDescent="0.2">
@@ -8828,10 +8828,10 @@
         <v>7</v>
       </c>
       <c r="C838" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D838" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="839" spans="1:4" x14ac:dyDescent="0.2">
@@ -8839,7 +8839,7 @@
         <v>9</v>
       </c>
       <c r="C839" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="840" spans="1:4" x14ac:dyDescent="0.2">
@@ -8992,7 +8992,7 @@
         <v>9</v>
       </c>
       <c r="C854" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D854" s="3"/>
     </row>
@@ -9014,13 +9014,13 @@
     </row>
     <row r="858" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A858" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B858" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C858" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="859" spans="1:4" x14ac:dyDescent="0.2">
@@ -9028,7 +9028,7 @@
         <v>9</v>
       </c>
       <c r="C859" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="860" spans="1:4" x14ac:dyDescent="0.2">
@@ -9036,7 +9036,7 @@
         <v>4</v>
       </c>
       <c r="C860" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="861" spans="1:4" x14ac:dyDescent="0.2">
@@ -9044,10 +9044,10 @@
         <v>7</v>
       </c>
       <c r="C861" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D861" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="862" spans="1:4" x14ac:dyDescent="0.2">
@@ -9055,10 +9055,10 @@
         <v>7</v>
       </c>
       <c r="C862" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D862" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="863" spans="1:4" x14ac:dyDescent="0.2">
@@ -9066,7 +9066,7 @@
         <v>9</v>
       </c>
       <c r="C863" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="864" spans="1:4" x14ac:dyDescent="0.2">
@@ -9219,7 +9219,7 @@
         <v>9</v>
       </c>
       <c r="C878" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D878" s="3"/>
     </row>
@@ -9241,13 +9241,13 @@
     </row>
     <row r="882" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A882" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B882" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C882" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="883" spans="1:4" x14ac:dyDescent="0.2">
@@ -9255,7 +9255,7 @@
         <v>9</v>
       </c>
       <c r="C883" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="884" spans="1:4" x14ac:dyDescent="0.2">
@@ -9263,7 +9263,7 @@
         <v>4</v>
       </c>
       <c r="C884" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="885" spans="1:4" x14ac:dyDescent="0.2">
@@ -9271,10 +9271,10 @@
         <v>7</v>
       </c>
       <c r="C885" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D885" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="886" spans="1:4" x14ac:dyDescent="0.2">
@@ -9282,10 +9282,10 @@
         <v>7</v>
       </c>
       <c r="C886" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D886" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="887" spans="1:4" x14ac:dyDescent="0.2">
@@ -9293,7 +9293,7 @@
         <v>9</v>
       </c>
       <c r="C887" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="888" spans="1:4" x14ac:dyDescent="0.2">
@@ -9446,7 +9446,7 @@
         <v>9</v>
       </c>
       <c r="C902" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D902" s="3"/>
     </row>
@@ -9468,13 +9468,13 @@
     </row>
     <row r="906" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A906" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B906" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C906" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="907" spans="1:4" x14ac:dyDescent="0.2">
@@ -9482,7 +9482,7 @@
         <v>9</v>
       </c>
       <c r="C907" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="908" spans="1:4" x14ac:dyDescent="0.2">
@@ -9490,7 +9490,7 @@
         <v>4</v>
       </c>
       <c r="C908" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="909" spans="1:4" x14ac:dyDescent="0.2">
@@ -9498,10 +9498,10 @@
         <v>7</v>
       </c>
       <c r="C909" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D909" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="910" spans="1:4" x14ac:dyDescent="0.2">
@@ -9509,10 +9509,10 @@
         <v>7</v>
       </c>
       <c r="C910" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D910" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="911" spans="1:4" x14ac:dyDescent="0.2">
@@ -9520,7 +9520,7 @@
         <v>9</v>
       </c>
       <c r="C911" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="912" spans="1:4" x14ac:dyDescent="0.2">
@@ -9704,7 +9704,7 @@
         <v>9</v>
       </c>
       <c r="C929" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D929" s="3"/>
     </row>
@@ -9726,7 +9726,7 @@
     </row>
     <row r="933" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A933" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B933" s="2" t="s">
         <v>4</v>
@@ -9748,7 +9748,7 @@
         <v>4</v>
       </c>
       <c r="C935" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="936" spans="1:4" x14ac:dyDescent="0.2">
@@ -9756,10 +9756,10 @@
         <v>7</v>
       </c>
       <c r="C936" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D936" s="2" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
     </row>
     <row r="937" spans="1:4" x14ac:dyDescent="0.2">
@@ -9767,7 +9767,7 @@
         <v>7</v>
       </c>
       <c r="C937" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D937" s="2" t="s">
         <v>41</v>
@@ -9778,7 +9778,7 @@
         <v>9</v>
       </c>
       <c r="C938" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="939" spans="1:4" x14ac:dyDescent="0.2">
@@ -9786,7 +9786,7 @@
         <v>4</v>
       </c>
       <c r="C939" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="940" spans="1:4" x14ac:dyDescent="0.2">
@@ -9799,7 +9799,7 @@
         <v>4</v>
       </c>
       <c r="C941" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="942" spans="1:4" x14ac:dyDescent="0.2">
@@ -9807,7 +9807,7 @@
         <v>9</v>
       </c>
       <c r="C942" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="943" spans="1:4" x14ac:dyDescent="0.2">
@@ -9815,7 +9815,7 @@
         <v>9</v>
       </c>
       <c r="C943" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="944" spans="1:4" x14ac:dyDescent="0.2">
@@ -9832,7 +9832,7 @@
     </row>
     <row r="946" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A946" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B946" s="2" t="s">
         <v>4</v>
@@ -9854,7 +9854,7 @@
         <v>4</v>
       </c>
       <c r="C948" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="949" spans="1:4" x14ac:dyDescent="0.2">
@@ -9862,10 +9862,10 @@
         <v>7</v>
       </c>
       <c r="C949" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D949" s="2" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
     </row>
     <row r="950" spans="1:4" x14ac:dyDescent="0.2">
@@ -9873,7 +9873,7 @@
         <v>7</v>
       </c>
       <c r="C950" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D950" s="2" t="s">
         <v>41</v>
@@ -9884,7 +9884,7 @@
         <v>9</v>
       </c>
       <c r="C951" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="952" spans="1:4" x14ac:dyDescent="0.2">
@@ -9892,7 +9892,7 @@
         <v>4</v>
       </c>
       <c r="C952" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="953" spans="1:4" x14ac:dyDescent="0.2">
@@ -9905,7 +9905,7 @@
         <v>4</v>
       </c>
       <c r="C954" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="955" spans="1:4" x14ac:dyDescent="0.2">
@@ -9913,7 +9913,7 @@
         <v>9</v>
       </c>
       <c r="C955" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="956" spans="1:4" x14ac:dyDescent="0.2">
@@ -9921,7 +9921,7 @@
         <v>4</v>
       </c>
       <c r="C956" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
